--- a/老虎机数学专题-机率新手除错指南.xlsx
+++ b/老虎机数学专题-机率新手除错指南.xlsx
@@ -5183,6 +5183,9 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:BF173" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -5604,5 +5607,8 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:I61" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>